--- a/Templates/bulkImport/config/construct_PUBC_config_sabah.xlsx
+++ b/Templates/bulkImport/config/construct_PUBC_config_sabah.xlsx
@@ -4,17 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9024"/>
+    <workbookView windowWidth="28800" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="construct_PUBC_config_sabah" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
   <si>
     <t>*</t>
   </si>
@@ -22,25 +37,49 @@
     <t>show</t>
   </si>
   <si>
-    <t>Show</t>
-  </si>
-  <si>
     <t>c_date_received</t>
   </si>
   <si>
     <t>c_time_received</t>
   </si>
   <si>
+    <t>c_aging</t>
+  </si>
+  <si>
     <t>c_date_acknowledgement</t>
   </si>
   <si>
+    <t>c_complaint_closing_date</t>
+  </si>
+  <si>
+    <t>c_source</t>
+  </si>
+  <si>
+    <t>c_date_source</t>
+  </si>
+  <si>
+    <t>c_ref_no</t>
+  </si>
+  <si>
     <t>c_received_by</t>
   </si>
   <si>
-    <t>c_source</t>
-  </si>
-  <si>
-    <t>c_ref_no</t>
+    <t>c_record_id</t>
+  </si>
+  <si>
+    <t>c_info_remarks</t>
+  </si>
+  <si>
+    <t>c_reprted_by</t>
+  </si>
+  <si>
+    <t>c_contact_no</t>
+  </si>
+  <si>
+    <t>c_email</t>
+  </si>
+  <si>
+    <t>c_requestor_address</t>
   </si>
   <si>
     <t>c_chainage_from</t>
@@ -49,6 +88,15 @@
     <t>c_chainage_to</t>
   </si>
   <si>
+    <t>c_coordinate_from</t>
+  </si>
+  <si>
+    <t>c_coordinate_to</t>
+  </si>
+  <si>
+    <t>c_location</t>
+  </si>
+  <si>
     <t>c_category</t>
   </si>
   <si>
@@ -64,131 +112,277 @@
     <t>c_photo</t>
   </si>
   <si>
+    <t>c_videos</t>
+  </si>
+  <si>
+    <t>c_cc_user</t>
+  </si>
+  <si>
+    <t>c_cc_remarks</t>
+  </si>
+  <si>
+    <t>c_action</t>
+  </si>
+  <si>
+    <t>c_action_status</t>
+  </si>
+  <si>
+    <t>c_actioner</t>
+  </si>
+  <si>
+    <t>c_action_date</t>
+  </si>
+  <si>
+    <t>c_assign_action</t>
+  </si>
+  <si>
+    <t>c_instruction</t>
+  </si>
+  <si>
+    <t>c_date_assign</t>
+  </si>
+  <si>
+    <t>c_assign_file</t>
+  </si>
+  <si>
+    <t>c_timeline</t>
+  </si>
+  <si>
+    <t>c_verify_date</t>
+  </si>
+  <si>
+    <t>c_expect_complete_date</t>
+  </si>
+  <si>
+    <t>c_update_action</t>
+  </si>
+  <si>
+    <t>c_update_progress</t>
+  </si>
+  <si>
+    <t>c_update_remark</t>
+  </si>
+  <si>
+    <t>c_updated_by</t>
+  </si>
+  <si>
+    <t>c_organization</t>
+  </si>
+  <si>
+    <t>c_recommend</t>
+  </si>
+  <si>
+    <t>c_recommend_remarks</t>
+  </si>
+  <si>
+    <t>c_verify_action</t>
+  </si>
+  <si>
+    <t>c_update_file</t>
+  </si>
+  <si>
+    <t>c_verify_remarks</t>
+  </si>
+  <si>
+    <t>c_satisfactory_level</t>
+  </si>
+  <si>
+    <t>c_close_file</t>
+  </si>
+  <si>
+    <t>c_close_remarks</t>
+  </si>
+  <si>
+    <t>c_closed_by</t>
+  </si>
+  <si>
+    <t>c_time_spent</t>
+  </si>
+  <si>
+    <t>c_date_close</t>
+  </si>
+  <si>
+    <t>c_close_action</t>
+  </si>
+  <si>
+    <t>Date Received</t>
+  </si>
+  <si>
+    <t>Time Received</t>
+  </si>
+  <si>
+    <t>Aging</t>
+  </si>
+  <si>
+    <t>Date of Acknowledgement</t>
+  </si>
+  <si>
+    <t>Date of Closing Complaint</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Source Date</t>
+  </si>
+  <si>
+    <t>Source Reference No.</t>
+  </si>
+  <si>
+    <t>Received By</t>
+  </si>
+  <si>
+    <t>PBC Ref No.</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Reported By</t>
+  </si>
+  <si>
+    <t>Contact No.</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Chainage (From)</t>
+  </si>
+  <si>
+    <t>Chainage (To)</t>
+  </si>
+  <si>
+    <t>Coordinate (From)</t>
+  </si>
+  <si>
+    <t>Coordinate (To)</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Documents</t>
+  </si>
+  <si>
+    <t>Photos</t>
+  </si>
+  <si>
+    <t>Videos</t>
+  </si>
+  <si>
+    <t>CC User</t>
+  </si>
+  <si>
+    <t>CC Remarks</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Actioner</t>
+  </si>
+  <si>
+    <t>Action Date</t>
+  </si>
+  <si>
+    <t>Assign to Actionee?</t>
+  </si>
+  <si>
+    <t>Instruction</t>
+  </si>
+  <si>
+    <t>Date of SOR Instructions to Rectify Work</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>Timeline</t>
+  </si>
+  <si>
+    <t>Verification Date</t>
+  </si>
+  <si>
+    <t>Expected Completion Date</t>
+  </si>
+  <si>
+    <t>Additional Details</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Recommend To</t>
+  </si>
+  <si>
+    <t>Verify Action</t>
+  </si>
+  <si>
+    <t>Requestor Satisfactory Level</t>
+  </si>
+  <si>
+    <t>File (Close)</t>
+  </si>
+  <si>
+    <t>Closed By</t>
+  </si>
+  <si>
+    <t>Time Spent</t>
+  </si>
+  <si>
+    <t>Date Close</t>
+  </si>
+  <si>
+    <t>Action Close</t>
+  </si>
+  <si>
     <t>c_video</t>
-  </si>
-  <si>
-    <t>c_update_action</t>
-  </si>
-  <si>
-    <t>c_updated_by</t>
-  </si>
-  <si>
-    <t>c_action</t>
-  </si>
-  <si>
-    <t>c_action_status</t>
-  </si>
-  <si>
-    <t>c_actioner</t>
-  </si>
-  <si>
-    <t>c_action_date</t>
-  </si>
-  <si>
-    <t>c_close_file</t>
-  </si>
-  <si>
-    <t>c_close_remarks</t>
-  </si>
-  <si>
-    <t>c_closed_by</t>
-  </si>
-  <si>
-    <t>c_date_close</t>
-  </si>
-  <si>
-    <t>c_close_action</t>
-  </si>
-  <si>
-    <t>Date Received</t>
-  </si>
-  <si>
-    <t>Time Received</t>
-  </si>
-  <si>
-    <t>Date of Acknowledgement to Complaint</t>
-  </si>
-  <si>
-    <t>Received By</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Source Reference No.</t>
-  </si>
-  <si>
-    <t>Chainage (From)</t>
-  </si>
-  <si>
-    <t>Chainage (To)</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Documents</t>
-  </si>
-  <si>
-    <t>Photos</t>
-  </si>
-  <si>
-    <t>Videos</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Updated By</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Action Status</t>
-  </si>
-  <si>
-    <t>Actioner</t>
-  </si>
-  <si>
-    <t>Action Date</t>
-  </si>
-  <si>
-    <t>Close File</t>
-  </si>
-  <si>
-    <t>Close Remarks</t>
-  </si>
-  <si>
-    <t>Closed By</t>
-  </si>
-  <si>
-    <t>Date Close</t>
-  </si>
-  <si>
-    <t>Close Action</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-&quot;RM&quot;* #,##0.00_-;\-&quot;RM&quot;* #,##0.00_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;RM&quot;* #,##0_-;\-&quot;RM&quot;* #,##0_-;_-&quot;RM&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFCCCCCC"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -647,28 +841,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -677,124 +862,140 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1143,94 +1344,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:BD5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
   <cols>
-    <col min="1" max="2" width="15.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="37.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.1111111111111" customWidth="1"/>
+    <col min="1" max="2" width="14.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="12.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="12.2222222222222" customWidth="1"/>
     <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
-    <col min="6" max="6" width="20.4444444444444" customWidth="1"/>
-    <col min="7" max="7" width="16.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="13.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="10.4444444444444" customWidth="1"/>
-    <col min="10" max="10" width="12.8888888888889" customWidth="1"/>
-    <col min="11" max="11" width="9.44444444444444" customWidth="1"/>
-    <col min="12" max="12" width="11.8888888888889" customWidth="1"/>
-    <col min="13" max="13" width="8.11111111111111" customWidth="1"/>
-    <col min="14" max="14" width="7.88888888888889" customWidth="1"/>
-    <col min="15" max="15" width="15.6666666666667" customWidth="1"/>
-    <col min="16" max="16" width="13.5555555555556" customWidth="1"/>
-    <col min="17" max="17" width="8.33333333333333" customWidth="1"/>
-    <col min="18" max="19" width="10.1111111111111" customWidth="1"/>
-    <col min="20" max="20" width="13.4444444444444" customWidth="1"/>
-    <col min="21" max="21" width="11.4444444444444" customWidth="1"/>
-    <col min="22" max="22" width="14.6666666666667" customWidth="1"/>
-    <col min="23" max="23" width="11.6666666666667" customWidth="1"/>
+    <col min="6" max="6" width="8.11111111111111" customWidth="1"/>
+    <col min="7" max="7" width="12.7777777777778" customWidth="1"/>
+    <col min="8" max="8" width="8.11111111111111" customWidth="1"/>
+    <col min="9" max="9" width="9.55555555555556" customWidth="1"/>
+    <col min="10" max="10" width="10.4444444444444" customWidth="1"/>
+    <col min="11" max="11" width="8.55555555555556" customWidth="1"/>
+    <col min="12" max="12" width="11.5555555555556" customWidth="1"/>
+    <col min="13" max="13" width="7.33333333333333" customWidth="1"/>
+    <col min="14" max="14" width="7.11111111111111" customWidth="1"/>
+    <col min="15" max="15" width="15.2222222222222" customWidth="1"/>
+    <col min="16" max="16" width="13.3333333333333" customWidth="1"/>
+    <col min="17" max="17" width="8" customWidth="1"/>
+    <col min="18" max="19" width="9.88888888888889" customWidth="1"/>
+    <col min="20" max="20" width="9.33333333333333" customWidth="1"/>
+    <col min="21" max="21" width="9.77777777777778" customWidth="1"/>
+    <col min="22" max="22" width="11.6666666666667" customWidth="1"/>
+    <col min="23" max="23" width="8.55555555555556" customWidth="1"/>
+    <col min="24" max="24" width="8.22222222222222" customWidth="1"/>
+    <col min="25" max="25" width="7.55555555555556" customWidth="1"/>
+    <col min="26" max="26" width="7.88888888888889" customWidth="1"/>
+    <col min="27" max="27" width="8.88888888888889" customWidth="1"/>
+    <col min="28" max="28" width="8.66666666666667" customWidth="1"/>
+    <col min="29" max="29" width="7.77777777777778" customWidth="1"/>
+    <col min="30" max="32" width="8.77777777777778" customWidth="1"/>
+    <col min="33" max="33" width="8.55555555555556" customWidth="1"/>
+    <col min="34" max="34" width="8.77777777777778" customWidth="1"/>
+    <col min="35" max="35" width="8.33333333333333" customWidth="1"/>
+    <col min="36" max="36" width="8.55555555555556" customWidth="1"/>
+    <col min="37" max="38" width="8.22222222222222" customWidth="1"/>
+    <col min="39" max="39" width="8.44444444444444" customWidth="1"/>
+    <col min="40" max="40" width="8.33333333333333" customWidth="1"/>
+    <col min="41" max="41" width="8.66666666666667" customWidth="1"/>
+    <col min="42" max="43" width="8.33333333333333" customWidth="1"/>
+    <col min="44" max="44" width="8.55555555555556" customWidth="1"/>
+    <col min="45" max="45" width="7.88888888888889" customWidth="1"/>
+    <col min="46" max="46" width="8" customWidth="1"/>
+    <col min="47" max="47" width="8.22222222222222" customWidth="1"/>
+    <col min="48" max="48" width="8.33333333333333" customWidth="1"/>
+    <col min="49" max="50" width="8.88888888888889" customWidth="1"/>
+    <col min="51" max="51" width="9" customWidth="1"/>
+    <col min="52" max="52" width="8.55555555555556" customWidth="1"/>
+    <col min="53" max="53" width="8.88888888888889" customWidth="1"/>
+    <col min="54" max="55" width="8.66666666666667" customWidth="1"/>
+    <col min="56" max="56" width="8.88888888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" t="s">
         <v>0</v>
       </c>
       <c r="I1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:56">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" t="s">
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="s">
         <v>1</v>
@@ -1245,22 +1485,115 @@
         <v>1</v>
       </c>
       <c r="U2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:56">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1336,159 +1669,438 @@
       <c r="Y3">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" t="s">
+      <c r="Z3">
+        <v>25</v>
+      </c>
+      <c r="AA3">
+        <v>26</v>
+      </c>
+      <c r="AB3">
+        <v>27</v>
+      </c>
+      <c r="AC3">
+        <v>28</v>
+      </c>
+      <c r="AD3">
+        <v>29</v>
+      </c>
+      <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
+        <v>31</v>
+      </c>
+      <c r="AG3">
+        <v>32</v>
+      </c>
+      <c r="AH3">
+        <v>33</v>
+      </c>
+      <c r="AI3">
+        <v>34</v>
+      </c>
+      <c r="AJ3">
+        <v>35</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>37</v>
+      </c>
+      <c r="AM3">
+        <v>38</v>
+      </c>
+      <c r="AN3">
+        <v>39</v>
+      </c>
+      <c r="AO3">
+        <v>40</v>
+      </c>
+      <c r="AP3">
+        <v>41</v>
+      </c>
+      <c r="AQ3">
+        <v>42</v>
+      </c>
+      <c r="AR3">
+        <v>43</v>
+      </c>
+      <c r="AS3">
+        <v>44</v>
+      </c>
+      <c r="AT3">
+        <v>45</v>
+      </c>
+      <c r="AU3">
+        <v>46</v>
+      </c>
+      <c r="AV3">
+        <v>47</v>
+      </c>
+      <c r="AW3">
+        <v>48</v>
+      </c>
+      <c r="AX3">
+        <v>49</v>
+      </c>
+      <c r="AY3">
+        <v>50</v>
+      </c>
+      <c r="AZ3">
+        <v>51</v>
+      </c>
+      <c r="BA3">
+        <v>52</v>
+      </c>
+      <c r="BB3">
+        <v>53</v>
+      </c>
+      <c r="BC3">
+        <v>54</v>
+      </c>
+      <c r="BD3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="1" ht="43.2" spans="1:56">
+      <c r="A4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="R4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="AA4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD4" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:56">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="J5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="L5" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="M5" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="N5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="O5" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="P5" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="Q5" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="R5" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="S5" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="T5" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="V5" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="X5" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="Y5" t="s">
-        <v>52</v>
+        <v>82</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>85</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>86</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>92</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>94</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>95</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>96</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>98</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>100</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>101</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>102</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>103</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>68</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>104</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>105</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1496,4 +2108,384 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetData>
+    <row r="1" ht="43.2" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" ht="43.2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" ht="57.6" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" ht="57.6" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="28.8" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="28.8" spans="1:6">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" ht="28.8" spans="1:6">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28.8" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" ht="28.8" spans="1:6">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="28.8" spans="1:6">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" ht="28.8" spans="1:6">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" ht="28.8" spans="1:6">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" ht="43.2" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" ht="43.2" spans="1:6">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" ht="28.8" spans="1:6">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" ht="43.2" spans="1:6">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="43.2" spans="1:6">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" ht="28.8" spans="1:6">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" ht="28.8" spans="1:6">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" ht="28.8" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" ht="28.8" spans="1:6">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:6">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" ht="28.8" spans="1:6">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" ht="28.8" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" ht="28.8" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" ht="28.8" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" ht="43.2" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" ht="28.8" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" ht="28.8" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" ht="43.2" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" ht="28.8" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" ht="28.8" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" ht="28.8" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="37" ht="28.8" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" ht="28.8" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="39" ht="57.6" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" ht="43.2" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" ht="43.2" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" ht="43.2" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" ht="28.8" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" ht="28.8" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" ht="28.8" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" ht="43.2" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" ht="43.2" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="48" ht="28.8" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" ht="43.2" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" ht="43.2" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="51" ht="28.8" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" ht="28.8" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" ht="43.2" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" ht="28.8" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" ht="28.8" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="56" ht="28.8" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" ht="13" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>